--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20260813.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_会議体・意見聴取" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_課題・リスク" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_変更管理・打合せ記録" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_仕様書対応表" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1393,28 +1394,786 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>条項</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>仕様書の記載内容（原文）</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>対応する作業（01_WBS）</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>作業数</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>網羅</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>目的・期間</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>障がいのある人が自立した生活のもと安心して暮らすことができるとともに、障がいのある人もない人も一人の人間として尊重され、互いに思いやりを持って生き生きと暮らせるまちづくりを進めるため、国が定める基本指針や県の計画、当町の現行計画を踏まえ、おのまち障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画を策定するものとする。</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>前提条項</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>目的・期間</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>契約締結日から令和9年3月25日まで（※公告第1-36号は令和9年3月31日）</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>前提条項</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>目的・期間</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>スケジュール。6月 業者選定・契約締結／〜7月 アンケート調査・統計整理／〜8月 アンケート調査・課題分析（自立支援協議会による検討）／9月 骨子案作成／10月 骨子案検討（自立支援協議会による検討）／〜12月 素案作成／〜1月 素案検討（自立支援協議会による検討・パブリックコメントの実施）／〜2月 計画書承認・校正・計画書完成／3月 契約完了</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>6-2 骨子案の協議（自立支援協議会）
+6-6 素案の協議（自立支援協議会）
+7-2 パブリックコメントの実施</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>5(1)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>障がい者ニーズ調査。アンケート調査により、障がい福祉サービスの実態や障がい者の意向などを把握し分析・課題の抽出等を行う。単純集計の他、性別・年齢別・障がい別・地域別等の必要なクロス集計、自由回答のとりまとめを含めて行い、町の現状や課題などを抽出・把握し、計画策定のための基礎資料となるものと位置づける。アンケート等の作成及び発送については受託者が実施する。受託者はアンケート等回収票の開封、データ入力、集計、分析、課題整理を行う。なお、アンケート等の送付数は600件程度であり、回収数は400件程度を見込んでいる。</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>1-5 町への資料依頼票の作成
+1-6 町データの受領
+2-2 調査実施設計</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①ア</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（ア）調査内容の企画</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>2-1 調査内容の企画</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①イ</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（イ）調査票の作成</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>2-3 調査票の作成と補修正</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①ウ</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（ウ）調査用品の準備・印刷。※印刷物は墨印刷とする。発送封筒は角2封筒、返送は長3封筒（テープ加工）を用いる。※対象者の抽出は当町にて行い、受託者が宛名ラベルの作成を行う。</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>2-6 調査用品の準備・印刷</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①エ</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（エ）調査の実施（郵送での発送返送）</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>2-8 調査の発送・回収</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①オ</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（オ）御礼を兼ねた督促はがきの発送準備</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>2-9 督促はがきの準備・発送</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①カ</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（カ）御礼を兼ねた督促はがきの発送</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>2-9 督促はがきの準備・発送</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①キ</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（キ）回収票点検〜データ入力（自由意見の入力整理）〜チェック〜集計</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>2-10 回収票の点検・ナンバリング・データ入力</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>5(1)①ク</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>委託事項（ク）分析（単純集計・クロス集計からの分析）</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>2-11 集計・分析</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>作業分担表</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>2-4 調査票原案の町の確認
+2-5 対象者の抽出
+2-7 宛名ラベルの作成
+4-2 町による報告書の確認</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>5(3)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>1-3 現行計画（第7期・第3期）の確認
+1-4 第3期地域福祉計画との役割分担の整理
+3-1 実施計画と質問票の作成
+3-2 対象先の選定
+3-3 依頼の送付・日程調整
+3-4 ヒアリングの実施
+3-5 記録の作成と対象先への確認
+5-1 現行計画の取組み状況の検証
+5-2 手帳所持者・サービス利用状況の分析
+5-3 課題の抽出
+5-4 人口推計の出典の統一</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>5(4)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>6-1 骨子案の作成
+6-2 骨子案の協議（自立支援協議会）
+6-3 成果目標の設定
+6-4 サービス見込量の算定
+6-5 素案の作成
+6-6 素案の協議（自立支援協議会）
+8-1 計画案の作成</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>委託業務の内容</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>5(5)</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>パブリックコメントの実施支援。計画素案がほぼ完成した段階で、町ウェブサイトを活用したパブリックコメントの実施を支援（実施アドバイス、意見への対応検討）し、結果を計画案へ反映する。パブリックコメントの実施時期については、当町と協議の上、決定することとする。</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>7-1 パブリックコメントの様式作成
+7-2 パブリックコメントの実施
+7-3 意見への対応</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>成果品①</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>①アンケート調査結果及びヒアリング調査結果報告書　電子データ</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>3-1 実施計画と質問票の作成
+4-1 アンケート調査結果及びヒアリング調査結果報告書の作成
+4-3 報告書の完成・納品</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>成果品②</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>②障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画　電子データ。※原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む。※電子データはMicrosoft Word 2019以上の形式で収録すること。</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>8-2 レイアウトデザイン・イラスト起こし
+8-3 リライト作業
+8-4 納品・検収</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>打合せ・その他</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>8①</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>打合せは必要に応じて随時行い、受託者が打ち合わせ内容の記録を作成し当町と相互に確認する。</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>1-7 工程変更の協議と打合せ記録の作成</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>打合せ・その他</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>8②</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>当町で開催する自立支援協議会（3回）に出席し、計画の説明をする。</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>7-4 自立支援協議会への出席（3回）</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>打合せ・その他</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>11④</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>本仕様書について定めのない事項等が生じた場合、または本業務履行上、基本事項の変更の必要が認められた場合には、当町と受託者間で双方協議の上、定めるものとする。</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>1-7 工程変更の協議と打合せ記録の作成</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>打合せ・その他</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>公告10⑥</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>自治体の当該計画策定や調査研究実績があり、本計画策定の実務を担う者（公告第1-36号 10⑥）</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>1-1 契約・体制の確立、キックオフ</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>※ 「要確認」は、01_WBS に対応する作業が置かれていない条項です。業務の抜けを疑ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>※ 「前提条項」は、目的・計画期間・個人情報の取扱いなど、作業として分解せず業務全体で担保する条項です。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1440,45 +2199,50 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>仕様書根拠</t>
+          <t>仕様書 条項</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>仕様書の記載内容（原文）</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>担当</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>予定開始</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>予定完了</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>進捗率</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>重み</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>実績・根拠</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>前提条件・ブロッカー</t>
         </is>
@@ -1505,43 +2269,48 @@
           <t>実施体制、役割分担</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>公告10⑥</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>【公告10⑥】自治体の当該計画策定や調査研究実績があり、本計画策定の実務を担う者（公告第1-36号 10⑥）</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
+      <c r="J2" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J2" s="19" t="n">
+      <c r="K2" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="K2" s="20" t="n">
+      <c r="L2" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L2" s="16" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>キックオフ資料・業務計画書</t>
         </is>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1568,43 +2337,48 @@
           <t>成果品要件・工程・作業分担の確定</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>仕様書全般</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J3" s="19" t="n">
+      <c r="K3" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="L3" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="16" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>仕様書適合性チェック 第2版（00_引継ぎ）</t>
         </is>
       </c>
-      <c r="M3" s="16" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1631,43 +2405,48 @@
           <t>3部構成、9分野の施策体系</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I4" s="18" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="K4" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="K4" s="20" t="n">
+      <c r="L4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>計画接続マトリクス（02_キックオフ）</t>
         </is>
       </c>
-      <c r="M4" s="16" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1694,43 +2473,48 @@
           <t>地域共生社会、重層的支援体制、成年後見制度利用促進の切り分け</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="K5" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="L5" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="16" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>地域福祉計画との整合確認メモ</t>
         </is>
       </c>
-      <c r="M5" s="16" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1757,43 +2541,48 @@
           <t>障がい分7項目＋確認事項</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)】障がい者ニーズ調査。アンケート調査により、障がい福祉サービスの実態や障がい者の意向などを把握し分析・課題の抽出等を行う。単純集計の他、性別・年齢別・障がい別・地域別等の必要なクロス集計、自由回答のとりまとめを含めて行い、町の現状や課題などを抽出・把握し、計画策定のための基礎資料となるものと位置づける。アンケート等の作成及び発送については受託者が実施する。受託者はアンケート等回収票の開封、データ入力、集計、分析、課題整理を行う。なお、アンケート等の送付数は600件程度であり、回収数は400件程度を見込んでいる。</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
+      <c r="K6" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="L6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>小野町_データ依頼票 04_障がい計画（16_町データ依頼）</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1820,43 +2609,48 @@
           <t>サービス実績、セルフプラン、対象者数等</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)】障がい者ニーズ調査。アンケート調査により、障がい福祉サービスの実態や障がい者の意向などを把握し分析・課題の抽出等を行う。単純集計の他、性別・年齢別・障がい別・地域別等の必要なクロス集計、自由回答のとりまとめを含めて行い、町の現状や課題などを抽出・把握し、計画策定のための基礎資料となるものと位置づける。アンケート等の作成及び発送については受託者が実施する。受託者はアンケート等回収票の開封、データ入力、集計、分析、課題整理を行う。なお、アンケート等の送付数は600件程度であり、回収数は400件程度を見込んでいる。</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="K7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="L7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>受領0件／依頼7件</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="N7" s="16" t="inlineStr">
         <is>
           <t>**町の回答。P2・P5・P6が依存する**</t>
         </is>
@@ -1865,63 +2659,69 @@
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>工程変更の協議と打合せ記録の作成</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>設問設計、クロス集計軸、見込量への接続表</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)①ア</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>仕様書7の工程から3〜4か月遅れているため、変更を町と協議し記録化する。**記録の作成は仕様書8①により受託者の義務**</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>仕様書11④・仕様書8①</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>【11④】本仕様書について定めのない事項等が生じた場合、または本業務履行上、基本事項の変更の必要が認められた場合には、当町と受託者間で双方協議の上、定めるものとする。
+【8①】打合せは必要に応じて随時行い、受託者が打ち合わせ内容の記録を作成し当町と相互に確認する。</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>アンケート接続表（04_算定・見込量）</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**工程変更協議資料と打合せ記録様式を作成済み（02_キックオフ・業務計画）**</t>
+        </is>
+      </c>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>**町との協議。8月19日の協議会またはその前後に行う**</t>
         </is>
       </c>
     </row>
@@ -1933,56 +2733,61 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>抽出条件案、回収率67％の逆算工程、調査用品の仕様、集計方針</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
+          <t>設問設計、クロス集計軸、見込量への接続表</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)①ア</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)①ア】委託事項（ア）調査内容の企画</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="K9" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="L9" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>**障がい者ニーズ調査実施設計書（15_ヒアリング・調査設計）。**回収率を9要素に分解し、9月中旬発送の逆算工程を作成</t>
-        </is>
-      </c>
       <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>アンケート接続表（04_算定・見込量）</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1996,58 +2801,63 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>★0727版の児童用に28箇所以上の本文欠落。一般用も問番号・条件見出し・ルビ13件</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)①イ</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
+          <t>抽出条件案、回収率67％の逆算工程、調査用品の仕様、集計方針</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)】障がい者ニーズ調査。アンケート調査により、障がい福祉サービスの実態や障がい者の意向などを把握し分析・課題の抽出等を行う。単純集計の他、性別・年齢別・障がい別・地域別等の必要なクロス集計、自由回答のとりまとめを含めて行い、町の現状や課題などを抽出・把握し、計画策定のための基礎資料となるものと位置づける。アンケート等の作成及び発送については受託者が実施する。受託者はアンケート等回収票の開封、データ入力、集計、分析、課題整理を行う。なお、アンケート等の送付数は600件程度であり、回収数は400件程度を見込んでいる。</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>分岐案は実施設計書3-4に整理（一般用の先行発送を含む）</t>
-        </is>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>**★0727版が手元にない（依頼票D1）。工程全体の律速**</t>
+          <t>**障がい者ニーズ調査実施設計書（15_ヒアリング・調査設計）。**回収率を9要素に分解し、9月中旬発送の逆算工程を作成</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2059,58 +2869,63 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>町による内容確認</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>作業分担表（発注者）</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>町</t>
+          <t>★0727版の児童用に28箇所以上の本文欠落。一般用も問番号・条件見出し・ルビ13件</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)①イ</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)①イ】委託事項（イ）調査票の作成</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>調査票の復元</t>
+          <t>分岐案は実施設計書3-4に整理（一般用の先行発送を含む）</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>**★0727版が手元にない（依頼票D1）。工程全体の律速**</t>
         </is>
       </c>
     </row>
@@ -2122,58 +2937,63 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>対象者の抽出</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>送付600件。手帳所持者508人では届かず対象拡大が必要</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
+          <t>町による内容確認</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>作業分担表（発注者）</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>**抽出条件案（区分①〜⑩）を作成済み**</t>
-        </is>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>**町による区分ごとの実数の回答（依頼票D2）。所管課をまたぐ照会で2〜3週間**</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>調査票の復元</t>
         </is>
       </c>
     </row>
@@ -2185,58 +3005,63 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>対象者の抽出</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>墨印刷、角2封筒、長3封筒（テープ加工）</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)①ウ</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>送付600件。手帳所持者508人では届かず対象拡大が必要</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>作業分担表（発注者）</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>仕様は実施設計書4-1に整理</t>
-        </is>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>調査票の確定。**墨印刷でのルビ可読性は実物校正が必要**</t>
+          <t>**抽出条件案（区分①〜⑩）を作成済み**</t>
+        </is>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>**町による区分ごとの実数の回答（依頼票D2）。所管課をまたぐ照会で2〜3週間**</t>
         </is>
       </c>
     </row>
@@ -2248,58 +3073,63 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>対象者抽出後</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>作業分担表（受託者）</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
+          <t>墨印刷、角2封筒、長3封筒（テープ加工）</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)①ウ</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)①ウ】委託事項（ウ）調査用品の準備・印刷。※印刷物は墨印刷とする。発送封筒は角2封筒、返送は長3封筒（テープ加工）を用いる。※対象者の抽出は当町にて行い、受託者が宛名ラベルの作成を行う。</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="K14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L14" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="M14" s="16" t="inlineStr">
         <is>
-          <t>対象者の抽出</t>
+          <t>仕様は実施設計書4-1に整理</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>調査票の確定。**墨印刷でのルビ可読性は実物校正が必要**</t>
         </is>
       </c>
     </row>
@@ -2311,58 +3141,63 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>送付600件程度・有効回収400件程度（回収率約67％）</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)①エ</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
+          <t>対象者抽出後</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>作業分担表（受託者）</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="K15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>逆算工程は作成済み（9月中旬発送）</t>
-        </is>
+      <c r="L15" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="M15" s="16" t="inlineStr">
         <is>
-          <t>調査票の確定、対象者の抽出</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>対象者の抽出</t>
         </is>
       </c>
     </row>
@@ -2374,58 +3209,63 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>督促はがきの準備・発送</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>締切の3〜5日前に投函</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)①オ・カ</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
+          <t>送付600件程度・有効回収400件程度（回収率約67％）</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)①エ</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)①エ】委託事項（エ）調査の実施（郵送での発送返送）</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="K16" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>逆算工程に織り込み済み</t>
-        </is>
+      <c r="L16" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="M16" s="16" t="inlineStr">
         <is>
-          <t>**前回調査で督促を行ったかが未確認（依頼票D3）。行っていた場合は12.4ptを督促以外で作る必要がある**</t>
+          <t>逆算工程は作成済み（9月中旬発送）</t>
+        </is>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>調査票の確定、対象者の抽出</t>
         </is>
       </c>
     </row>
@@ -2437,58 +3277,64 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>回収票の点検・ナンバリング・データ入力</t>
+          <t>督促はがきの準備・発送</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>自由回答を含む</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)①キ</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
+          <t>締切の3〜5日前に投函</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)①オ・カ</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)①オ】委託事項（オ）御礼を兼ねた督促はがきの発送準備
+【5(1)①カ】委託事項（カ）御礼を兼ねた督促はがきの発送</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="K17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L17" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="M17" s="16" t="inlineStr">
         <is>
-          <t>調査の回収</t>
+          <t>逆算工程に織り込み済み</t>
+        </is>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>**前回調査で督促を行ったかが未確認（依頼票D3）。行っていた場合は12.4ptを督促以外で作る必要がある**</t>
         </is>
       </c>
     </row>
@@ -2500,121 +3346,131 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>回収票の点検・ナンバリング・データ入力</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>単純集計、性別・年齢別・障がい別・地域別のクロス集計、自由回答</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(1)①ク</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
+          <t>自由回答を含む</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)①キ</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)①キ】委託事項（キ）回収票点検〜データ入力（自由意見の入力整理）〜チェック〜集計</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" s="20" t="n">
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>**集計方針を確定（集計軸9種に性別を追加、少数セルの扱い、前回調査との比較の管理）。**仕様の明示要件である性別が接続表に欠けていた点を解消</t>
-        </is>
-      </c>
       <c r="M18" s="16" t="inlineStr">
         <is>
-          <t>データ入力の完了。地域別集計の粒度の確認（依頼票C12）</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>調査の回収</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>対象6区分、質問票6種（大問35・小問102）</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(3)・成果品①</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
+          <t>単純集計、性別・年齢別・障がい別・地域別のクロス集計、自由回答</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(1)①ク</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>【5(1)①ク】委託事項（ク）分析（単純集計・クロス集計からの分析）</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="K19" s="20" t="n">
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>**関係者団体等ヒアリング実施計画書（15_ヒアリング・調査設計）。**アンケートで数えられる事項は聞かず、供給側にしか答えられない事項に絞った</t>
-        </is>
-      </c>
       <c r="M19" s="16" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**集計方針を確定（集計軸9種に性別を追加、少数セルの扱い、前回調査との比較の管理）。**仕様の明示要件である性別が接続表に欠けていた点を解消</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>データ入力の完了。地域別集計の粒度の確認（依頼票C12）</t>
         </is>
       </c>
     </row>
@@ -2626,58 +3482,64 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>対象先の選定</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>小野町の方の利用実績が多い先から優先</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(3)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+          <t>対象6区分、質問票6種（大問35・小問102）</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(3)・成果品①</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。
+【成果品①】①アンケート調査結果及びヒアリング調査結果報告書　電子データ</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L20" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>**関係者団体等ヒアリング実施計画書（15_ヒアリング・調査設計）。**アンケートで数えられる事項は聞かず、供給側にしか答えられない事項に絞った</t>
+        </is>
+      </c>
+      <c r="N20" s="16" t="inlineStr">
         <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>**町のサービス実績（町内外事業所別・依頼票D4）**</t>
         </is>
       </c>
     </row>
@@ -2689,58 +3551,63 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>依頼の送付・日程調整</t>
+          <t>対象先の選定</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>依頼文、質問票、個人情報の取扱いの事前送付</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
+          <t>小野町の方の利用実績が多い先から優先</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
+          <t>受託者・町</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="K21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>依頼文の記載事項は実施計画書に整理</t>
-        </is>
+      <c r="L21" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="M21" s="16" t="inlineStr">
         <is>
-          <t>対象先の選定</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>**町のサービス実績（町内外事業所別・依頼票D4）**</t>
         </is>
       </c>
     </row>
@@ -2752,58 +3619,63 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>依頼の送付・日程調整</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>20〜27件。アンケートの発送・回収と並行</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
+          <t>依頼文、質問票、個人情報の取扱いの事前送付</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J22" s="19" t="n">
+      <c r="K22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L22" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="M22" s="16" t="inlineStr">
         <is>
-          <t>日程調整</t>
+          <t>依頼文の記載事項は実施計画書に整理</t>
+        </is>
+      </c>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>対象先の選定</t>
         </is>
       </c>
     </row>
@@ -2815,121 +3687,131 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>要点記録、引用の可否の確認</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
+          <t>20〜27件。アンケートの発送・回収と並行</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J23" s="19" t="n">
+      <c r="K23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>記録の様式は実施計画書に整理</t>
-        </is>
+      <c r="L23" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="M23" s="16" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>日程調整</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>調査結果とヒアリング結果を1本の報告書にまとめる</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>仕様書6 成果品①</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
+          <t>要点記録、引用の可否の確認</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(3)</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J24" s="19" t="n">
+      <c r="K24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L24" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="M24" s="16" t="inlineStr">
         <is>
-          <t>**集計の完了、ヒアリング記録の完成**</t>
+          <t>記録の様式は実施計画書に整理</t>
+        </is>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
@@ -2941,58 +3823,63 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>作業分担表で町の作業</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>作業分担表（発注者）</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>町</t>
+          <t>調査結果とヒアリング結果を1本の報告書にまとめる</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>仕様書6 成果品①</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>【成果品①】①アンケート調査結果及びヒアリング調査結果報告書　電子データ</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H25" s="17" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J25" s="19" t="n">
+      <c r="K25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
+      <c r="L25" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>報告書の作成</t>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>**集計の完了、ヒアリング記録の完成**</t>
         </is>
       </c>
     </row>
@@ -3004,121 +3891,131 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>電子データ</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>仕様書6 成果品①</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>作業分担表で町の作業</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>作業分担表（発注者）</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J26" s="19" t="n">
+      <c r="K26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="20" t="n">
+      <c r="L26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="L26" s="16" t="inlineStr">
+      <c r="M26" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M26" s="16" t="inlineStr">
-        <is>
-          <t>町の確認</t>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>第7期の成果目標・活動指標の実績</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(3)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
+          <t>電子データ</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>仕様書6 成果品①</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>【成果品①】①アンケート調査結果及びヒアリング調査結果報告書　電子データ</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I27" s="23" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K27" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>前回アンケート（280件・22件）の検証と計画接続マトリクスを作成済み</t>
-        </is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="M27" s="16" t="inlineStr">
         <is>
-          <t>町のサービス実績（依頼票D4・D7）</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
@@ -3130,58 +4027,63 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>手帳所持者508人（身体372・療育74・精神62）。支給決定量と実利用量</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
+          <t>第7期の成果目標・活動指標の実績</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I28" s="23" t="inlineStr">
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
       </c>
-      <c r="J28" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" s="20" t="n">
+      <c r="K28" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L28" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L28" s="16" t="inlineStr">
-        <is>
-          <t>手帳所持者数の推移は取得済み（令和5年539人→令和7年508人）</t>
-        </is>
-      </c>
       <c r="M28" s="16" t="inlineStr">
         <is>
-          <t>町のサービス実績（依頼票D4）</t>
+          <t>前回アンケート（280件・22件）の検証と計画接続マトリクスを作成済み</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>町のサービス実績（依頼票D4・D7）</t>
         </is>
       </c>
     </row>
@@ -3193,58 +4095,63 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>課題の抽出</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>調査結果・ヒアリング結果を踏まえた課題整理</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
+          <t>手帳所持者508人（身体372・療育74・精神62）。支給決定量と実利用量</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="20" t="n">
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L29" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L29" s="16" t="inlineStr">
-        <is>
-          <t>現時点の課題15項目を骨子案に整理済み（相談支援体制、経済的負担、医療・通院、移動・外出、防災、家族介助者、18歳移行、就労、権利擁護 ほか）</t>
-        </is>
-      </c>
       <c r="M29" s="16" t="inlineStr">
         <is>
-          <t>調査結果・ヒアリング結果</t>
+          <t>手帳所持者数の推移は取得済み（令和5年539人→令和7年508人）</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>町のサービス実績（依頼票D4）</t>
         </is>
       </c>
     </row>
@@ -3256,121 +4163,131 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>課題の抽出</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>高齢者計画は見える化（社人研）、障がい計画は地域福祉計画（コーホート変化率法）。最大310人・3.4％の差</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
+          <t>調査結果・ヒアリング結果を踏まえた課題整理</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16" t="inlineStr">
-        <is>
-          <t>差異を特定済み</t>
-        </is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="L30" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>**8月19日の自立支援協議会で協議し統一する**</t>
+          <t>現時点の課題15項目を骨子案に整理済み（相談支援体制、経済的負担、医療・通院、移動・外出、防災、家族介助者、18歳移行、就労、権利擁護 ほか）</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>調査結果・ヒアリング結果</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>3部構成。成果目標を国の8分野に対応</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(4)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>高齢者計画は見える化（社人研）、障がい計画は地域福祉計画（コーホート変化率法）。最大310人・3.4％の差</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(3)</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I31" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>60</v>
-      </c>
-      <c r="K31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" s="16" t="inlineStr">
-        <is>
-          <t>初版を作成済み（09_骨子案・4部構成）。見込量の算定方式も設定</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L31" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="M31" s="16" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>差異を特定済み</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>**8月19日の自立支援協議会で協議し統一する**</t>
         </is>
       </c>
     </row>
@@ -3382,58 +4299,63 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>第2回に諮る</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(4)・7</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+          <t>3部構成。成果目標を国の8分野に対応</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(4)</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="16" t="inlineStr">
-        <is>
-          <t>**仕様書7では10月の回。工程変更により12月に統合する案を協議中**</t>
-        </is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="L32" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>初版を作成済み（09_骨子案・4部構成）。見込量の算定方式も設定</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
@@ -3445,58 +4367,64 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>国の基本指針の8分野</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(4)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
+          <t>第2回に諮る</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(4)・7</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）
+【7】スケジュール。6月 業者選定・契約締結／〜7月 アンケート調査・統計整理／〜8月 アンケート調査・課題分析（自立支援協議会による検討）／9月 骨子案作成／10月 骨子案検討（自立支援協議会による検討）／〜12月 素案作成／〜1月 素案検討（自立支援協議会による検討・パブリックコメントの実施）／〜2月 計画書承認・校正・計画書完成／3月 契約完了</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J33" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J33" s="19" t="n">
+      <c r="K33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="16" t="inlineStr">
-        <is>
-          <t>枠組みは骨子案に設定済み</t>
-        </is>
+      <c r="L33" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="M33" s="16" t="inlineStr">
         <is>
-          <t>**セルフプラン件数・相談支援専門員数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
+          <t>**仕様書7では10月の回。工程変更により12月に統合する案を協議中**</t>
+        </is>
+      </c>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -3508,58 +4436,63 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>サービス種類別の見込量</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
+          <t>国の基本指針の8分野</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
+          <t>受託者・町</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J34" s="19" t="n">
+      <c r="K34" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" s="16" t="inlineStr">
-        <is>
-          <t>算定方式は骨子案に設定済み</t>
-        </is>
+      <c r="L34" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="M34" s="16" t="inlineStr">
         <is>
-          <t>**町のサービス実績（依頼票D4・D7）、ヒアリング結果**</t>
+          <t>枠組みは骨子案に設定済み</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>**セルフプラン件数・相談支援専門員数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
       </c>
     </row>
@@ -3571,58 +4504,63 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>3計画一体の素案</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
+          <t>サービス種類別の見込量</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="I35" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J35" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K35" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" s="16" t="inlineStr">
-        <is>
-          <t>**引継ぎ時点の拡充版のまま（03_計画素案）。第2版への改訂が未着手**</t>
-        </is>
+      <c r="J35" s="21" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="M35" s="16" t="inlineStr">
         <is>
-          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
+          <t>算定方式は骨子案に設定済み</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>**町のサービス実績（依頼票D4・D7）、ヒアリング結果**</t>
         </is>
       </c>
     </row>
@@ -3634,121 +4572,132 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>第3回に諮る</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(4)・7</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+          <t>3計画一体の素案</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(4)</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L36" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="M36" s="16" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>**引継ぎ時点の拡充版のまま（03_計画素案）。第2版への改訂が未着手**</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>実施要領、意見提出様式、対応表</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(5)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>第3回に諮る</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(4)・7</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）
+【7】スケジュール。6月 業者選定・契約締結／〜7月 アンケート調査・統計整理／〜8月 アンケート調査・課題分析（自立支援協議会による検討）／9月 骨子案作成／10月 骨子案検討（自立支援協議会による検討）／〜12月 素案作成／〜1月 素案検討（自立支援協議会による検討・パブリックコメントの実施）／〜2月 計画書承認・校正・計画書完成／3月 契約完了</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="K37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="16" t="inlineStr">
-        <is>
-          <t>計画策定業務設計書 第4章（高齢者計画と共通）</t>
-        </is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="J37" s="21" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="M37" s="16" t="inlineStr">
         <is>
           <t>―</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -3760,58 +4709,63 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>意見提出期間1か月</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(5)・7</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>町</t>
+          <t>実施要領、意見提出様式、対応表</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(5)</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>【5(5)】パブリックコメントの実施支援。計画素案がほぼ完成した段階で、町ウェブサイトを活用したパブリックコメントの実施を支援（実施アドバイス、意見への対応検討）し、結果を計画案へ反映する。パブリックコメントの実施時期については、当町と協議の上、決定することとする。</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L38" s="16" t="inlineStr">
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="L38" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>計画策定業務設計書 第4章（高齢者計画と共通）</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
         <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="M38" s="16" t="inlineStr">
-        <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -3823,58 +4777,64 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>意見の整理、対応案の作成、計画への反映</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(5)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>意見提出期間1か月</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(5)・7</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>【5(5)】パブリックコメントの実施支援。計画素案がほぼ完成した段階で、町ウェブサイトを活用したパブリックコメントの実施を支援（実施アドバイス、意見への対応検討）し、結果を計画案へ反映する。パブリックコメントの実施時期については、当町と協議の上、決定することとする。
+【7】スケジュール。6月 業者選定・契約締結／〜7月 アンケート調査・統計整理／〜8月 アンケート調査・課題分析（自立支援協議会による検討）／9月 骨子案作成／10月 骨子案検討（自立支援協議会による検討）／〜12月 素案作成／〜1月 素案検討（自立支援協議会による検討・パブリックコメントの実施）／〜2月 計画書承認・校正・計画書完成／3月 契約完了</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>町</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="I39" s="21" t="inlineStr">
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="J39" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J39" s="19" t="n">
+      <c r="K39" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="20" t="n">
+      <c r="L39" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L39" s="16" t="inlineStr">
-        <is>
-          <t>対応表の様式は作成済み</t>
-        </is>
-      </c>
       <c r="M39" s="16" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -3886,121 +4846,131 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>仕様書8②により3回と明記</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>仕様書8②</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
+          <t>意見の整理、対応案の作成、計画への反映</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(5)</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>【5(5)】パブリックコメントの実施支援。計画素案がほぼ完成した段階で、町ウェブサイトを活用したパブリックコメントの実施を支援（実施アドバイス、意見への対応検討）し、結果を計画案へ反映する。パブリックコメントの実施時期については、当町と協議の上、決定することとする。</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I40" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K40" s="20" t="n">
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L40" s="16" t="inlineStr">
-        <is>
-          <t>第1回は令和8年8月19日（資料第3版を作成済み）</t>
-        </is>
-      </c>
       <c r="M40" s="16" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>対応表の様式は作成済み</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>パブリックコメント対応後の計画案</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>仕様書5(4)</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
+          <t>仕様書8②により3回と明記</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>仕様書8②</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>【8②】当町で開催する自立支援協議会（3回）に出席し、計画の説明をする。</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="I41" s="21" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="L41" s="20" t="n">
+        <v>2</v>
       </c>
       <c r="M41" s="16" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>第1回は令和8年8月19日（資料第3版を作成済み）</t>
+        </is>
+      </c>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
@@ -4012,58 +4982,63 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>**仕様書は「原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む」と定める**</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>仕様書6 成果品②</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
+          <t>パブリックコメント対応後の計画案</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>仕様書5(4)</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="H42" s="17" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I42" s="21" t="inlineStr">
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="J42" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J42" s="19" t="n">
+      <c r="K42" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="20" t="n">
+      <c r="L42" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L42" s="16" t="inlineStr">
+      <c r="M42" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M42" s="16" t="inlineStr">
-        <is>
-          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -4075,58 +5050,63 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>読みやすさの調整</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
+          <t>**仕様書は「原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む」と定める**</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>仕様書6 成果品②</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>【成果品②】②障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画　電子データ。※原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む。※電子データはMicrosoft Word 2019以上の形式で収録すること。</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I43" s="21" t="inlineStr">
+      <c r="J43" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J43" s="19" t="n">
+      <c r="K43" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="16" t="inlineStr">
+      <c r="L43" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M43" s="16" t="inlineStr">
-        <is>
-          <t>計画案の確定</t>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
       </c>
     </row>
@@ -4138,64 +5118,137 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
+          <t>8-3</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>リライト作業</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>読みやすさの調整</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>仕様書6 成果品②</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>【成果品②】②障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画　電子データ。※原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む。※電子データはMicrosoft Word 2019以上の形式で収録すること。</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J44" s="21" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>計画案の確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>P8 完成・納品</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
           <t>8-4</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>納品・検収</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>電子データ（Microsoft Word 2019以上の形式）。**印刷の指定はなし**</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>仕様書6 成果品②</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>【成果品②】②障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画　電子データ。※原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む。※電子データはMicrosoft Word 2019以上の形式で収録すること。</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="G44" s="17" t="inlineStr">
+      <c r="H45" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="H44" s="17" t="inlineStr">
+      <c r="I45" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I44" s="21" t="inlineStr">
+      <c r="J45" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J44" s="19" t="n">
+      <c r="K45" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="20" t="n">
+      <c r="L45" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="L44" s="16" t="inlineStr">
+      <c r="M45" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M44" s="16" t="inlineStr">
+      <c r="N45" s="16" t="inlineStr">
         <is>
           <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M44"/>
-  <conditionalFormatting sqref="J2:J44">
+  <autoFilter ref="A1:N45"/>
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>100</formula>
     </cfRule>
@@ -4204,10 +5257,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,進行中,要対応,データ待ち,未着手"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="K2:K45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -4222,7 +5275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4302,31 +5355,31 @@
         </is>
       </c>
       <c r="B2" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A2)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A2,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A2,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A2,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A2,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A2,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A2)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A2)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A2)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I2" s="17" t="inlineStr">
@@ -4352,31 +5405,31 @@
         </is>
       </c>
       <c r="B3" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A3)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A3,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A3,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A3,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A3,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A3,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A3)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A3)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A3)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I3" s="17" t="inlineStr">
@@ -4402,31 +5455,31 @@
         </is>
       </c>
       <c r="B4" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A4)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A4,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A4,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A4,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A4,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A4,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A4)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A4)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A4)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I4" s="17" t="inlineStr">
@@ -4452,31 +5505,31 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A5)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A5,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A5,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A5,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A5,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A5,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A5)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A5)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A5)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -4502,31 +5555,31 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A6)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A6,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A6,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A6,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A6,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A6,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A6)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A6)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A6)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I6" s="17" t="inlineStr">
@@ -4552,31 +5605,31 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A7)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A7,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A7,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A7,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A7,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A7,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A7)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A7)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A7)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -4602,31 +5655,31 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A8)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A8,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A8,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A8,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A8,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A8,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A8)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A8)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A8)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -4652,31 +5705,31 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>COUNTIF('01_WBS'!$A$2:$A$44,$A9)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$45,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A9,'01_WBS'!$I$2:$I$44,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A9,'01_WBS'!$I$2:$I$44,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A9,'01_WBS'!$I$2:$I$44,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A9,'01_WBS'!$I$2:$I$44,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$44,$A9,'01_WBS'!$I$2:$I$44,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A9)*'01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A9)*'01_WBS'!$J$2:$J$44*'01_WBS'!$K$2:$K$44)/SUMPRODUCT(('01_WBS'!$A$2:$A$44=$A9)*'01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I9" s="17" t="inlineStr">
@@ -4726,7 +5779,7 @@
         <v/>
       </c>
       <c r="H10" s="27">
-        <f>IF(SUM('01_WBS'!$K$2:$K$44)=0,0,SUMPRODUCT('01_WBS'!$J$2:$J$44,'01_WBS'!$K$2:$K$44)/SUM('01_WBS'!$K$2:$K$44)/100)</f>
+        <f>IF(SUM('01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT('01_WBS'!$K$2:$K$45,'01_WBS'!$L$2:$L$45)/SUM('01_WBS'!$L$2:$L$45)/100)</f>
         <v/>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -4750,6 +5803,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>※ 各作業が仕様書のどの条項にあたるかは 01_WBS のE列・F列、条項の網羅状況は 09_仕様書対応表 を参照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>※ 01_WBS の「状態」「進捗率」を書き換えると、本表とダッシュボードが再計算されます。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20260813.xlsx
@@ -17,9 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_課題・リスク" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_変更管理・打合せ記録" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_仕様書対応表" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ブロック別進捗" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$O$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -600,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -855,299 +856,281 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>■ 仕様書の業務ブロック別</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>仕様書ブロック</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>作業数</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>加重進捗率</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>現況・律速</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6">
+        <f>'10_ブロック別進捗'!A2</f>
+        <v/>
+      </c>
+      <c r="B18" s="7">
+        <f>'10_ブロック別進捗'!C2</f>
+        <v/>
+      </c>
+      <c r="C18" s="8">
+        <f>'10_ブロック別進捗'!I2</f>
+        <v/>
+      </c>
+      <c r="D18" s="9">
+        <f>'10_ブロック別進捗'!J2</f>
+        <v/>
+      </c>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6">
+        <f>'10_ブロック別進捗'!A3</f>
+        <v/>
+      </c>
+      <c r="B19" s="7">
+        <f>'10_ブロック別進捗'!C3</f>
+        <v/>
+      </c>
+      <c r="C19" s="8">
+        <f>'10_ブロック別進捗'!I3</f>
+        <v/>
+      </c>
+      <c r="D19" s="9">
+        <f>'10_ブロック別進捗'!J3</f>
+        <v/>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6">
+        <f>'10_ブロック別進捗'!A4</f>
+        <v/>
+      </c>
+      <c r="B20" s="7">
+        <f>'10_ブロック別進捗'!C4</f>
+        <v/>
+      </c>
+      <c r="C20" s="8">
+        <f>'10_ブロック別進捗'!I4</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>'10_ブロック別進捗'!J4</f>
+        <v/>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6">
+        <f>'10_ブロック別進捗'!A5</f>
+        <v/>
+      </c>
+      <c r="B21" s="7">
+        <f>'10_ブロック別進捗'!C5</f>
+        <v/>
+      </c>
+      <c r="C21" s="8">
+        <f>'10_ブロック別進捗'!I5</f>
+        <v/>
+      </c>
+      <c r="D21" s="9">
+        <f>'10_ブロック別進捗'!J5</f>
+        <v/>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6">
+        <f>'10_ブロック別進捗'!A6</f>
+        <v/>
+      </c>
+      <c r="B22" s="7">
+        <f>'10_ブロック別進捗'!C6</f>
+        <v/>
+      </c>
+      <c r="C22" s="8">
+        <f>'10_ブロック別進捗'!I6</f>
+        <v/>
+      </c>
+      <c r="D22" s="9">
+        <f>'10_ブロック別進捗'!J6</f>
+        <v/>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6">
+        <f>'10_ブロック別進捗'!A7</f>
+        <v/>
+      </c>
+      <c r="B23" s="7">
+        <f>'10_ブロック別進捗'!C7</f>
+        <v/>
+      </c>
+      <c r="C23" s="8">
+        <f>'10_ブロック別進捗'!I7</f>
+        <v/>
+      </c>
+      <c r="D23" s="9">
+        <f>'10_ブロック別進捗'!J7</f>
+        <v/>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6">
+        <f>'10_ブロック別進捗'!A8</f>
+        <v/>
+      </c>
+      <c r="B24" s="7">
+        <f>'10_ブロック別進捗'!C8</f>
+        <v/>
+      </c>
+      <c r="C24" s="8">
+        <f>'10_ブロック別進捗'!I8</f>
+        <v/>
+      </c>
+      <c r="D24" s="9">
+        <f>'10_ブロック別進捗'!J8</f>
+        <v/>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
           <t>■ 現況</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>**障がい計画は仕様書7の工程から3〜4か月遅れている。**仕様書は調査を7月までに実施し、9月に骨子案、10月に骨子案検討としているが、調査票が確定せず調査は未実施である。</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>8月13日に、ヒアリングの実施計画書と質問票6種、障がい者ニーズ調査の実施設計書（600件の抽出条件案・回収率67％の逆算工程）、工程変更協議資料を作成した。**設計は整い、あとは調査票の確定を待つ状態にある。**</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>**関係者団体等ヒアリングは、仕様書5(3)及び成果品①が求める業務項目でありながら、これまで実施も計画もされていなかった。**実施計画書と質問票（大問35・小問102）を作成し、9月中旬〜10月下旬にアンケートと並行して実施する設計とした。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>**回収率は仕様書が66.7％を想定するのに対し、前回実績は54.3％である。**12.4ポイントの改善が必要で、督促だけでは埋まらない。回収率を9要素に分解し、9月中旬発送の逆算工程を置いた。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>**手帳所持者は508人まで減少しており、600件の配布には対象拡大が必要である。**自立支援医療・難病・サービス利用者・障がい児通所・特別支援学級で補う抽出条件案（区分①〜⑩）を作成した。抽出は町の作業であるため、区分ごとの実数の回答を待って確定する。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>**素案は引継ぎ時点の拡充版のまま第2版への改訂が未着手である。**これは外部の条件に依存せず着手できる唯一の残作業であり、次に着手する。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>■ 警戒事項</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="9" t="n">
+    <row r="36">
+      <c r="A36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>児童用調査票に28箇所以上の本文欠落</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>調査を発送できず、工程全体が遅延する</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>**★0727版が手元にない（依頼票D1）。**一般用を先行発送し児童用を2週間遅らせる分岐案を用意した</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>仕様書工程から3〜4か月の遅延</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>契約上の工程変更にあたる</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>**工程変更協議資料を作成済み。**仕様書11④により町と協議し、8①により打合せ記録として相互確認する</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>回収率66.7％の達成</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>前回実績54.3％から12.4ポイントの改善が必要。分析の代表性に関わる</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>回収率を9要素に分解。督促と期間の確保が要。**前回が督促込みだった場合は電子回答の併用が必須**</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>配布600件に対し手帳所持者は508人</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>母集団が600人に満たない可能性がある</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>**回収率で見るか回収数で見るかを抽出前に町と合意する。**事後の説明では達成不能な要件を負う</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>レイアウトデザイン・イラスト起こしが工程にない</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>仕様書6は成果品②に含むと定める。デザイン工程が確保されていない</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>令和9年2〜3月にデザイン工程を確保する。**引継ぎ資料でも触れられていなかった**</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>完了日が公告と仕様書で異なる</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>公告は令和9年3月31日、仕様書は3月25日。納期の認識齟齬</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>町に確認する（依頼票C1）</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>■ 直近のマイルストーン</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>時期</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>令和8年8月19日</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>自立支援協議会 第1回（前回計画の総括・動向・方向性）</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>資料第3版を作成済み</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>令和8年8月中</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>調査票の確定（児童用の本文復元）</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>**★0727版の入手**</t>
         </is>
       </c>
       <c r="E36" s="9" t="n"/>
@@ -1156,24 +1139,22 @@
       <c r="H36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>令和8年8月中</t>
-        </is>
+      <c r="A37" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>対象者抽出の照会（区分①〜⑩）</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>仕様書工程から3〜4か月の遅延</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>契約上の工程変更にあたる</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>抽出条件案は作成済み</t>
+          <t>**工程変更協議資料を作成済み。**仕様書11④により町と協議し、8①により打合せ記録として相互確認する</t>
         </is>
       </c>
       <c r="E37" s="9" t="n"/>
@@ -1182,24 +1163,22 @@
       <c r="H37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>令和8年8月下旬</t>
-        </is>
+      <c r="A38" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>町による調査票原案の確認</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>回収率66.7％の達成</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>前回実績54.3％から12.4ポイントの改善が必要。分析の代表性に関わる</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>調査票の確定</t>
+          <t>回収率を9要素に分解。督促と期間の確保が要。**前回が督促込みだった場合は電子回答の併用が必須**</t>
         </is>
       </c>
       <c r="E38" s="9" t="n"/>
@@ -1208,24 +1187,22 @@
       <c r="H38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>令和8年9月中旬</t>
-        </is>
+      <c r="A39" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>**調査票の発送（回収率確保の起点）**</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>配布600件に対し手帳所持者は508人</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>母集団が600人に満たない可能性がある</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>調査票と対象者の確定</t>
+          <t>**回収率で見るか回収数で見るかを抽出前に町と合意する。**事後の説明では達成不能な要件を負う</t>
         </is>
       </c>
       <c r="E39" s="9" t="n"/>
@@ -1234,24 +1211,22 @@
       <c r="H39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>令和8年9〜10月</t>
-        </is>
+      <c r="A40" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>関係者団体等ヒアリング（20〜27件）</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>レイアウトデザイン・イラスト起こしが工程にない</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>仕様書6は成果品②に含むと定める。デザイン工程が確保されていない</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>対象先の選定</t>
+          <t>令和9年2〜3月にデザイン工程を確保する。**引継ぎ資料でも触れられていなかった**</t>
         </is>
       </c>
       <c r="E40" s="9" t="n"/>
@@ -1260,24 +1235,22 @@
       <c r="H40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>令和8年10月上旬</t>
-        </is>
+      <c r="A41" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>督促はがきの発送、回答期限</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>完了日が公告と仕様書で異なる</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>公告は令和9年3月31日、仕様書は3月25日。納期の認識齟齬</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>発送</t>
+          <t>町に確認する（依頼票C1）</t>
         </is>
       </c>
       <c r="E41" s="9" t="n"/>
@@ -1285,109 +1258,320 @@
       <c r="G41" s="9" t="n"/>
       <c r="H41" s="9" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>令和8年12月</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>成果品①の完成、自立支援協議会 第2回（調査結果・骨子案・見込量）</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>集計とヒアリング記録</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-    </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>令和9年1月</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>素案の確定、パブリックコメント</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>■ 直近のマイルストーン</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>令和9年2月</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>自立支援協議会 第3回（最終案）</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>前提</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>令和9年3月</t>
+          <t>令和8年8月19日</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・リライト、納品</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>自立支援協議会 第1回（前回計画の総括・動向・方向性）</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>**完了日の確認が必要**</t>
+          <t>資料第3版を作成済み</t>
         </is>
       </c>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n"/>
       <c r="H45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>令和8年8月中</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>調査票の確定（児童用の本文復元）</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>**★0727版の入手**</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>令和8年8月中</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>対象者抽出の照会（区分①〜⑩）</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>抽出条件案は作成済み</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>令和8年8月下旬</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>町による調査票原案の確認</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>調査票の確定</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>令和8年9月中旬</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>**調査票の発送（回収率確保の起点）**</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>調査票と対象者の確定</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>令和8年9〜10月</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>関係者団体等ヒアリング（20〜27件）</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>対象先の選定</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>令和8年10月上旬</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>督促はがきの発送、回答期限</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>発送</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>令和8年12月</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>成果品①の完成、自立支援協議会 第2回（調査結果・骨子案・見込量）</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>集計とヒアリング記録</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>令和9年1月</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>素案の確定、パブリックコメント</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>令和9年2月</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>自立支援協議会 第3回（最終案）</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>令和9年3月</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>レイアウトデザイン・リライト、納品</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>**完了日の確認が必要**</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2151,29 +2335,481 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>仕様書ブロック</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>該当条項</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>作業数</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>加重進捗率</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>現況・律速</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>5(1)、5(1)①ア、5(1)①イ、5(1)①ウ、5(1)①エ、5(1)①オ ほか</t>
+        </is>
+      </c>
+      <c r="C2" s="17">
+        <f>COUNTIF('01_WBS'!$E$2:$E$45,$A2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A2,'01_WBS'!$K$2:$K$45,"完了")</f>
+        <v/>
+      </c>
+      <c r="E2" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A2,'01_WBS'!$K$2:$K$45,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F2" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A2,'01_WBS'!$K$2:$K$45,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G2" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A2,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H2" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A2,'01_WBS'!$K$2:$K$45,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I2" s="24">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A2)*'01_WBS'!$M$2:$M$45)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A2)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A2)*'01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>**実施設計は完了。★0727版が入手できず調査票が確定しないため発送できない**</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>5(3)</t>
+        </is>
+      </c>
+      <c r="C3" s="17">
+        <f>COUNTIF('01_WBS'!$E$2:$E$45,$A3)</f>
+        <v/>
+      </c>
+      <c r="D3" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A3,'01_WBS'!$K$2:$K$45,"完了")</f>
+        <v/>
+      </c>
+      <c r="E3" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A3,'01_WBS'!$K$2:$K$45,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F3" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A3,'01_WBS'!$K$2:$K$45,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G3" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A3,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H3" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A3,'01_WBS'!$K$2:$K$45,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I3" s="24">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A3)*'01_WBS'!$M$2:$M$45)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A3)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A3)*'01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>前回調査による検証は済み。今期調査・ヒアリングの結果待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>5(4)</t>
+        </is>
+      </c>
+      <c r="C4" s="17">
+        <f>COUNTIF('01_WBS'!$E$2:$E$45,$A4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A4,'01_WBS'!$K$2:$K$45,"完了")</f>
+        <v/>
+      </c>
+      <c r="E4" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A4,'01_WBS'!$K$2:$K$45,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F4" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A4,'01_WBS'!$K$2:$K$45,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G4" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A4,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H4" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A4,'01_WBS'!$K$2:$K$45,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I4" s="24">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A4)*'01_WBS'!$M$2:$M$45)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A4)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A4)*'01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>**骨子案は作成済み。素案の第2版改訂は外部条件に依存せず着手できるが未着手**</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>B4 パブリックコメントの実施支援</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>5(5)</t>
+        </is>
+      </c>
+      <c r="C5" s="17">
+        <f>COUNTIF('01_WBS'!$E$2:$E$45,$A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A5,'01_WBS'!$K$2:$K$45,"完了")</f>
+        <v/>
+      </c>
+      <c r="E5" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A5,'01_WBS'!$K$2:$K$45,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F5" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A5,'01_WBS'!$K$2:$K$45,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G5" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A5,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H5" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A5,'01_WBS'!$K$2:$K$45,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I5" s="24">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A5)*'01_WBS'!$M$2:$M$45)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A5)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A5)*'01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>様式は作成済み。実施時期の確定待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>B5 成果品の納品</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>成果品①、成果品②</t>
+        </is>
+      </c>
+      <c r="C6" s="17">
+        <f>COUNTIF('01_WBS'!$E$2:$E$45,$A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A6,'01_WBS'!$K$2:$K$45,"完了")</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A6,'01_WBS'!$K$2:$K$45,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F6" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A6,'01_WBS'!$K$2:$K$45,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G6" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A6,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H6" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A6,'01_WBS'!$K$2:$K$45,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I6" s="24">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A6)*'01_WBS'!$M$2:$M$45)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A6)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A6)*'01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>**成果品①はヒアリングの実施が前提。②はレイアウトデザイン工程が未確保**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>B6 業務管理・打合せ</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>2、4、7、8①、8②、11④ ほか</t>
+        </is>
+      </c>
+      <c r="C7" s="17">
+        <f>COUNTIF('01_WBS'!$E$2:$E$45,$A7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A7,'01_WBS'!$K$2:$K$45,"完了")</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A7,'01_WBS'!$K$2:$K$45,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A7,'01_WBS'!$K$2:$K$45,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A7,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A7,'01_WBS'!$K$2:$K$45,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I7" s="24">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A7)*'01_WBS'!$M$2:$M$45)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A7)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A7)*'01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>**仕様書工程から3〜4か月遅延。工程変更の協議と記録化が要対応**</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>B7 仕様書に定めのない作業</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>（該当条項なし）</t>
+        </is>
+      </c>
+      <c r="C8" s="17">
+        <f>COUNTIF('01_WBS'!$E$2:$E$45,$A8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A8,'01_WBS'!$K$2:$K$45,"完了")</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A8,'01_WBS'!$K$2:$K$45,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A8,'01_WBS'!$K$2:$K$45,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A8,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$45,$A8,'01_WBS'!$K$2:$K$45,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I8" s="24">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A8)*'01_WBS'!$M$2:$M$45)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A8)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$E$2:$E$45=$A8)*'01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>該当なし。仕様書のいずれかの条項に紐づかない作業が発生した場合はここに現れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr"/>
+      <c r="C9" s="26">
+        <f>SUM(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="26">
+        <f>SUM(D2:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="26">
+        <f>SUM(G2:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="26">
+        <f>SUM(H2:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="27">
+        <f>IF(SUM('01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$45,'01_WBS'!$M$2:$M$45)/SUM('01_WBS'!$M$2:$M$45)/100)</f>
+        <v/>
+      </c>
+      <c r="J9" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>※ 段階（02_段階サマリ）は業務の進み方の切り口、ブロックは委託契約上の業務単位の切り口です。同じ作業を別の軸で見ています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>※ 作業が複数の条項にまたがる場合は、先頭の条項が属するブロックに数えています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>※ 未分類の作業があります：[]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2199,50 +2835,55 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
+          <t>仕様書ブロック</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
           <t>仕様書 条項</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>仕様書の記載内容（原文）</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>予定開始</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>予定完了</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>進捗率</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>重み</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>実績・根拠</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>前提条件・ブロッカー</t>
         </is>
@@ -2269,48 +2910,53 @@
           <t>実施体制、役割分担</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>B6 業務管理・打合せ</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>公告10⑥</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>【公告10⑥】自治体の当該計画策定や調査研究実績があり、本計画策定の実務を担う者（公告第1-36号 10⑥）</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J2" s="18" t="inlineStr">
+      <c r="K2" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K2" s="19" t="n">
+      <c r="L2" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L2" s="20" t="n">
+      <c r="M2" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>キックオフ資料・業務計画書</t>
         </is>
       </c>
-      <c r="N2" s="16" t="inlineStr">
+      <c r="O2" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2337,48 +2983,53 @@
           <t>成果品要件・工程・作業分担の確定</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>B6 業務管理・打合せ</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>仕様書全般</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="L3" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L3" s="20" t="n">
+      <c r="M3" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M3" s="16" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>仕様書適合性チェック 第2版（00_引継ぎ）</t>
         </is>
       </c>
-      <c r="N3" s="16" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2405,48 +3056,53 @@
           <t>3部構成、9分野の施策体系</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="K4" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="L4" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L4" s="20" t="n">
+      <c r="M4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M4" s="16" t="inlineStr">
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t>計画接続マトリクス（02_キックオフ）</t>
         </is>
       </c>
-      <c r="N4" s="16" t="inlineStr">
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2473,48 +3129,53 @@
           <t>地域共生社会、重層的支援体制、成年後見制度利用促進の切り分け</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="L5" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L5" s="20" t="n">
+      <c r="M5" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="16" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t>地域福祉計画との整合確認メモ</t>
         </is>
       </c>
-      <c r="N5" s="16" t="inlineStr">
+      <c r="O5" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2541,48 +3202,53 @@
           <t>障がい分7項目＋確認事項</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>【5(1)】障がい者ニーズ調査。アンケート調査により、障がい福祉サービスの実態や障がい者の意向などを把握し分析・課題の抽出等を行う。単純集計の他、性別・年齢別・障がい別・地域別等の必要なクロス集計、自由回答のとりまとめを含めて行い、町の現状や課題などを抽出・把握し、計画策定のための基礎資料となるものと位置づける。アンケート等の作成及び発送については受託者が実施する。受託者はアンケート等回収票の開封、データ入力、集計、分析、課題整理を行う。なお、アンケート等の送付数は600件程度であり、回収数は400件程度を見込んでいる。</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="L6" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L6" s="20" t="n">
+      <c r="M6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t>小野町_データ依頼票 04_障がい計画（16_町データ依頼）</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2609,48 +3275,53 @@
           <t>サービス実績、セルフプラン、対象者数等</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>【5(1)】障がい者ニーズ調査。アンケート調査により、障がい福祉サービスの実態や障がい者の意向などを把握し分析・課題の抽出等を行う。単純集計の他、性別・年齢別・障がい別・地域別等の必要なクロス集計、自由回答のとりまとめを含めて行い、町の現状や課題などを抽出・把握し、計画策定のための基礎資料となるものと位置づける。アンケート等の作成及び発送については受託者が実施する。受託者はアンケート等回収票の開封、データ入力、集計、分析、課題整理を行う。なお、アンケート等の送付数は600件程度であり、回収数は400件程度を見込んでいる。</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="L7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="20" t="n">
+      <c r="M7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="N7" s="16" t="inlineStr">
         <is>
           <t>受領0件／依頼7件</t>
         </is>
       </c>
-      <c r="N7" s="16" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t>**町の回答。P2・P5・P6が依存する**</t>
         </is>
@@ -2677,49 +3348,54 @@
           <t>仕様書7の工程から3〜4か月遅れているため、変更を町と協議し記録化する。**記録の作成は仕様書8①により受託者の義務**</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>B6 業務管理・打合せ</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>仕様書11④・仕様書8①</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>【11④】本仕様書について定めのない事項等が生じた場合、または本業務履行上、基本事項の変更の必要が認められた場合には、当町と受託者間で双方協議の上、定めるものとする。
 【8①】打合せは必要に応じて随時行い、受託者が打ち合わせ内容の記録を作成し当町と相互に確認する。</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="L8" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="L8" s="20" t="n">
+      <c r="M8" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t>**工程変更協議資料と打合せ記録様式を作成済み（02_キックオフ・業務計画）**</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="O8" s="16" t="inlineStr">
         <is>
           <t>**町との協議。8月19日の協議会またはその前後に行う**</t>
         </is>
@@ -2746,48 +3422,53 @@
           <t>設問設計、クロス集計軸、見込量への接続表</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)①ア</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>【5(1)①ア】委託事項（ア）調査内容の企画</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K9" s="19" t="n">
+      <c r="L9" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="M9" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="16" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>アンケート接続表（04_算定・見込量）</t>
         </is>
       </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2814,48 +3495,53 @@
           <t>抽出条件案、回収率67％の逆算工程、調査用品の仕様、集計方針</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>【5(1)】障がい者ニーズ調査。アンケート調査により、障がい福祉サービスの実態や障がい者の意向などを把握し分析・課題の抽出等を行う。単純集計の他、性別・年齢別・障がい別・地域別等の必要なクロス集計、自由回答のとりまとめを含めて行い、町の現状や課題などを抽出・把握し、計画策定のための基礎資料となるものと位置づける。アンケート等の作成及び発送については受託者が実施する。受託者はアンケート等回収票の開封、データ入力、集計、分析、課題整理を行う。なお、アンケート等の送付数は600件程度であり、回収数は400件程度を見込んでいる。</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K10" s="19" t="n">
+      <c r="L10" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L10" s="20" t="n">
+      <c r="M10" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="16" t="inlineStr">
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>**障がい者ニーズ調査実施設計書（15_ヒアリング・調査設計）。**回収率を9要素に分解し、9月中旬発送の逆算工程を作成</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2882,48 +3568,53 @@
           <t>★0727版の児童用に28箇所以上の本文欠落。一般用も問番号・条件見出し・ルビ13件</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)①イ</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>【5(1)①イ】委託事項（イ）調査票の作成</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="K11" s="19" t="n">
+      <c r="L11" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="L11" s="20" t="n">
+      <c r="M11" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>分岐案は実施設計書3-4に整理（一般用の先行発送を含む）</t>
         </is>
       </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>**★0727版が手元にない（依頼票D1）。工程全体の律速**</t>
         </is>
@@ -2950,48 +3641,53 @@
           <t>町による内容確認</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>作業分担表（発注者）</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K12" s="19" t="n">
+      <c r="L12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="20" t="n">
+      <c r="M12" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="16" t="inlineStr">
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="O12" s="16" t="inlineStr">
         <is>
           <t>調査票の復元</t>
         </is>
@@ -3018,48 +3714,53 @@
           <t>送付600件。手帳所持者508人では届かず対象拡大が必要</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>作業分担表（発注者）</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K13" s="19" t="n">
+      <c r="L13" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="L13" s="20" t="n">
+      <c r="M13" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="16" t="inlineStr">
+      <c r="N13" s="16" t="inlineStr">
         <is>
           <t>**抽出条件案（区分①〜⑩）を作成済み**</t>
         </is>
       </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>**町による区分ごとの実数の回答（依頼票D2）。所管課をまたぐ照会で2〜3週間**</t>
         </is>
@@ -3086,48 +3787,53 @@
           <t>墨印刷、角2封筒、長3封筒（テープ加工）</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)①ウ</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>【5(1)①ウ】委託事項（ウ）調査用品の準備・印刷。※印刷物は墨印刷とする。発送封筒は角2封筒、返送は長3封筒（テープ加工）を用いる。※対象者の抽出は当町にて行い、受託者が宛名ラベルの作成を行う。</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K14" s="19" t="n">
+      <c r="L14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="20" t="n">
+      <c r="M14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="16" t="inlineStr">
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>仕様は実施設計書4-1に整理</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="O14" s="16" t="inlineStr">
         <is>
           <t>調査票の確定。**墨印刷でのルビ可読性は実物校正が必要**</t>
         </is>
@@ -3154,48 +3860,53 @@
           <t>対象者抽出後</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>作業分担表（受託者）</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr">
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K15" s="19" t="n">
+      <c r="L15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="20" t="n">
+      <c r="M15" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="N15" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N15" s="16" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>対象者の抽出</t>
         </is>
@@ -3222,48 +3933,53 @@
           <t>送付600件程度・有効回収400件程度（回収率約67％）</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)①エ</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>【5(1)①エ】委託事項（エ）調査の実施（郵送での発送返送）</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="L16" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="20" t="n">
+      <c r="M16" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M16" s="16" t="inlineStr">
+      <c r="N16" s="16" t="inlineStr">
         <is>
           <t>逆算工程は作成済み（9月中旬発送）</t>
         </is>
       </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>調査票の確定、対象者の抽出</t>
         </is>
@@ -3290,49 +4006,54 @@
           <t>締切の3〜5日前に投函</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)①オ・カ</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>【5(1)①オ】委託事項（オ）御礼を兼ねた督促はがきの発送準備
 【5(1)①カ】委託事項（カ）御礼を兼ねた督促はがきの発送</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
+      <c r="K17" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K17" s="19" t="n">
+      <c r="L17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="20" t="n">
+      <c r="M17" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="N17" s="16" t="inlineStr">
         <is>
           <t>逆算工程に織り込み済み</t>
         </is>
       </c>
-      <c r="N17" s="16" t="inlineStr">
+      <c r="O17" s="16" t="inlineStr">
         <is>
           <t>**前回調査で督促を行ったかが未確認（依頼票D3）。行っていた場合は12.4ptを督促以外で作る必要がある**</t>
         </is>
@@ -3359,48 +4080,53 @@
           <t>自由回答を含む</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)①キ</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>【5(1)①キ】委託事項（キ）回収票点検〜データ入力（自由意見の入力整理）〜チェック〜集計</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J18" s="21" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K18" s="19" t="n">
+      <c r="L18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="20" t="n">
+      <c r="M18" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="N18" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="O18" s="16" t="inlineStr">
         <is>
           <t>調査の回収</t>
         </is>
@@ -3427,48 +4153,53 @@
           <t>単純集計、性別・年齢別・障がい別・地域別のクロス集計、自由回答</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>仕様書5(1)①ク</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>【5(1)①ク】委託事項（ク）分析（単純集計・クロス集計からの分析）</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="L19" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="L19" s="20" t="n">
+      <c r="M19" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="N19" s="16" t="inlineStr">
         <is>
           <t>**集計方針を確定（集計軸9種に性別を追加、少数セルの扱い、前回調査との比較の管理）。**仕様の明示要件である性別が接続表に欠けていた点を解消</t>
         </is>
       </c>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>データ入力の完了。地域別集計の粒度の確認（依頼票C12）</t>
         </is>
@@ -3495,49 +4226,54 @@
           <t>対象6区分、質問票6種（大問35・小問102）</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)・成果品①</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。
 【成果品①】①アンケート調査結果及びヒアリング調査結果報告書　電子データ</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
+      <c r="K20" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K20" s="19" t="n">
+      <c r="L20" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="M20" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M20" s="16" t="inlineStr">
+      <c r="N20" s="16" t="inlineStr">
         <is>
           <t>**関係者団体等ヒアリング実施計画書（15_ヒアリング・調査設計）。**アンケートで数えられる事項は聞かず、供給側にしか答えられない事項に絞った</t>
         </is>
       </c>
-      <c r="N20" s="16" t="inlineStr">
+      <c r="O20" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3564,48 +4300,53 @@
           <t>小野町の方の利用実績が多い先から優先</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="K21" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K21" s="19" t="n">
+      <c r="L21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="20" t="n">
+      <c r="M21" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="N21" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N21" s="16" t="inlineStr">
+      <c r="O21" s="16" t="inlineStr">
         <is>
           <t>**町のサービス実績（町内外事業所別・依頼票D4）**</t>
         </is>
@@ -3632,48 +4373,53 @@
           <t>依頼文、質問票、個人情報の取扱いの事前送付</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="L22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="20" t="n">
+      <c r="M22" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="N22" s="16" t="inlineStr">
         <is>
           <t>依頼文の記載事項は実施計画書に整理</t>
         </is>
       </c>
-      <c r="N22" s="16" t="inlineStr">
+      <c r="O22" s="16" t="inlineStr">
         <is>
           <t>対象先の選定</t>
         </is>
@@ -3700,48 +4446,53 @@
           <t>20〜27件。アンケートの発送・回収と並行</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="K23" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K23" s="19" t="n">
+      <c r="L23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="20" t="n">
+      <c r="M23" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="N23" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N23" s="16" t="inlineStr">
+      <c r="O23" s="16" t="inlineStr">
         <is>
           <t>日程調整</t>
         </is>
@@ -3768,48 +4519,53 @@
           <t>要点記録、引用の可否の確認</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K24" s="19" t="n">
+      <c r="L24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="20" t="n">
+      <c r="M24" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M24" s="16" t="inlineStr">
+      <c r="N24" s="16" t="inlineStr">
         <is>
           <t>記録の様式は実施計画書に整理</t>
         </is>
       </c>
-      <c r="N24" s="16" t="inlineStr">
+      <c r="O24" s="16" t="inlineStr">
         <is>
           <t>ヒアリングの実施</t>
         </is>
@@ -3836,48 +4592,53 @@
           <t>調査結果とヒアリング結果を1本の報告書にまとめる</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>B5 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>仕様書6 成果品①</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>【成果品①】①アンケート調査結果及びヒアリング調査結果報告書　電子データ</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="H25" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="J25" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="K25" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K25" s="19" t="n">
+      <c r="L25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="20" t="n">
+      <c r="M25" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="N25" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N25" s="16" t="inlineStr">
+      <c r="O25" s="16" t="inlineStr">
         <is>
           <t>**集計の完了、ヒアリング記録の完成**</t>
         </is>
@@ -3904,48 +4665,53 @@
           <t>作業分担表で町の作業</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>B1 障がい者ニーズ調査</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>作業分担表（発注者）</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>【作業分担表】調査票原案の検討＝発注者／調査票原案の作成と補修正＝受託者／対象者抽出＝発注者／宛名ラベル作成・調査票の印刷・封筒の手配・ラベル貼付・発送回収経費負担（回収見込70％）・督促はがきの準備と発送・回収票開封・データ入力・集計・分析＝受託者／報告書の確認＝発注者／報告書の完成＝受託者</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K26" s="19" t="n">
+      <c r="L26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="20" t="n">
+      <c r="M26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M26" s="16" t="inlineStr">
+      <c r="N26" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N26" s="16" t="inlineStr">
+      <c r="O26" s="16" t="inlineStr">
         <is>
           <t>報告書の作成</t>
         </is>
@@ -3972,48 +4738,53 @@
           <t>電子データ</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>B5 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>仕様書6 成果品①</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>【成果品①】①アンケート調査結果及びヒアリング調査結果報告書　電子データ</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="K27" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K27" s="19" t="n">
+      <c r="L27" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="20" t="n">
+      <c r="M27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="N27" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
+      <c r="O27" s="16" t="inlineStr">
         <is>
           <t>町の確認</t>
         </is>
@@ -4040,48 +4811,53 @@
           <t>第7期の成果目標・活動指標の実績</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J28" s="23" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
       </c>
-      <c r="K28" s="19" t="n">
+      <c r="L28" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="L28" s="20" t="n">
+      <c r="M28" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M28" s="16" t="inlineStr">
+      <c r="N28" s="16" t="inlineStr">
         <is>
           <t>前回アンケート（280件・22件）の検証と計画接続マトリクスを作成済み</t>
         </is>
       </c>
-      <c r="N28" s="16" t="inlineStr">
+      <c r="O28" s="16" t="inlineStr">
         <is>
           <t>町のサービス実績（依頼票D4・D7）</t>
         </is>
@@ -4108,48 +4884,53 @@
           <t>手帳所持者508人（身体372・療育74・精神62）。支給決定量と実利用量</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="J29" s="17" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J29" s="23" t="inlineStr">
+      <c r="K29" s="23" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
       </c>
-      <c r="K29" s="19" t="n">
+      <c r="L29" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="L29" s="20" t="n">
+      <c r="M29" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M29" s="16" t="inlineStr">
+      <c r="N29" s="16" t="inlineStr">
         <is>
           <t>手帳所持者数の推移は取得済み（令和5年539人→令和7年508人）</t>
         </is>
       </c>
-      <c r="N29" s="16" t="inlineStr">
+      <c r="O29" s="16" t="inlineStr">
         <is>
           <t>町のサービス実績（依頼票D4）</t>
         </is>
@@ -4176,48 +4957,53 @@
           <t>調査結果・ヒアリング結果を踏まえた課題整理</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J30" s="20" t="inlineStr">
+      <c r="K30" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K30" s="19" t="n">
+      <c r="L30" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="L30" s="20" t="n">
+      <c r="M30" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M30" s="16" t="inlineStr">
+      <c r="N30" s="16" t="inlineStr">
         <is>
           <t>現時点の課題15項目を骨子案に整理済み（相談支援体制、経済的負担、医療・通院、移動・外出、防災、家族介助者、18歳移行、就労、権利擁護 ほか）</t>
         </is>
       </c>
-      <c r="N30" s="16" t="inlineStr">
+      <c r="O30" s="16" t="inlineStr">
         <is>
           <t>調査結果・ヒアリング結果</t>
         </is>
@@ -4244,48 +5030,53 @@
           <t>高齢者計画は見える化（社人研）、障がい計画は地域福祉計画（コーホート変化率法）。最大310人・3.4％の差</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>B2 現状分析と課題の整理</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>【5(3)】現状分析と課題の整理。現行計画の取組み状況及び課題の検証を行う。また、障がい者ニーズ調査結果や関係者団体等ヒアリング調査結果、当町が実施する関連調査等の結果、国や県の上位計画や各種施策、並びに当町が保有する各種データ等をもとに、障がい者を取り巻く環境の分析や課題の抽出を行う。</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="K31" s="19" t="n">
+      <c r="L31" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="L31" s="20" t="n">
+      <c r="M31" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M31" s="16" t="inlineStr">
+      <c r="N31" s="16" t="inlineStr">
         <is>
           <t>差異を特定済み</t>
         </is>
       </c>
-      <c r="N31" s="16" t="inlineStr">
+      <c r="O31" s="16" t="inlineStr">
         <is>
           <t>**8月19日の自立支援協議会で協議し統一する**</t>
         </is>
@@ -4312,48 +5103,53 @@
           <t>3部構成。成果目標を国の8分野に対応</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J32" s="20" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K32" s="19" t="n">
+      <c r="L32" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="L32" s="20" t="n">
+      <c r="M32" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M32" s="16" t="inlineStr">
+      <c r="N32" s="16" t="inlineStr">
         <is>
           <t>初版を作成済み（09_骨子案・4部構成）。見込量の算定方式も設定</t>
         </is>
       </c>
-      <c r="N32" s="16" t="inlineStr">
+      <c r="O32" s="16" t="inlineStr">
         <is>
           <t>調査結果の反映</t>
         </is>
@@ -4380,49 +5176,54 @@
           <t>第2回に諮る</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)・7</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）
 【7】スケジュール。6月 業者選定・契約締結／〜7月 アンケート調査・統計整理／〜8月 アンケート調査・課題分析（自立支援協議会による検討）／9月 骨子案作成／10月 骨子案検討（自立支援協議会による検討）／〜12月 素案作成／〜1月 素案検討（自立支援協議会による検討・パブリックコメントの実施）／〜2月 計画書承認・校正・計画書完成／3月 契約完了</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H33" s="17" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="J33" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J33" s="21" t="inlineStr">
+      <c r="K33" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K33" s="19" t="n">
+      <c r="L33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="20" t="n">
+      <c r="M33" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M33" s="16" t="inlineStr">
+      <c r="N33" s="16" t="inlineStr">
         <is>
           <t>**仕様書7では10月の回。工程変更により12月に統合する案を協議中**</t>
         </is>
       </c>
-      <c r="N33" s="16" t="inlineStr">
+      <c r="O33" s="16" t="inlineStr">
         <is>
           <t>工程変更の合意</t>
         </is>
@@ -4449,48 +5250,53 @@
           <t>国の基本指針の8分野</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J34" s="21" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K34" s="19" t="n">
+      <c r="L34" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="20" t="n">
+      <c r="M34" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M34" s="16" t="inlineStr">
+      <c r="N34" s="16" t="inlineStr">
         <is>
           <t>枠組みは骨子案に設定済み</t>
         </is>
       </c>
-      <c r="N34" s="16" t="inlineStr">
+      <c r="O34" s="16" t="inlineStr">
         <is>
           <t>**セルフプラン件数・相談支援専門員数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
@@ -4517,48 +5323,53 @@
           <t>サービス種類別の見込量</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H35" s="17" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="J35" s="21" t="inlineStr">
+      <c r="K35" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K35" s="19" t="n">
+      <c r="L35" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="20" t="n">
+      <c r="M35" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="M35" s="16" t="inlineStr">
+      <c r="N35" s="16" t="inlineStr">
         <is>
           <t>算定方式は骨子案に設定済み</t>
         </is>
       </c>
-      <c r="N35" s="16" t="inlineStr">
+      <c r="O35" s="16" t="inlineStr">
         <is>
           <t>**町のサービス実績（依頼票D4・D7）、ヒアリング結果**</t>
         </is>
@@ -4585,48 +5396,53 @@
           <t>3計画一体の素案</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="J36" s="20" t="inlineStr">
+      <c r="K36" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K36" s="19" t="n">
+      <c r="L36" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="L36" s="20" t="n">
+      <c r="M36" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="M36" s="16" t="inlineStr">
+      <c r="N36" s="16" t="inlineStr">
         <is>
           <t>**引継ぎ時点の拡充版のまま（03_計画素案）。第2版への改訂が未着手**</t>
         </is>
       </c>
-      <c r="N36" s="16" t="inlineStr">
+      <c r="O36" s="16" t="inlineStr">
         <is>
           <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
         </is>
@@ -4653,49 +5469,54 @@
           <t>第3回に諮る</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)・7</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）
 【7】スケジュール。6月 業者選定・契約締結／〜7月 アンケート調査・統計整理／〜8月 アンケート調査・課題分析（自立支援協議会による検討）／9月 骨子案作成／10月 骨子案検討（自立支援協議会による検討）／〜12月 素案作成／〜1月 素案検討（自立支援協議会による検討・パブリックコメントの実施）／〜2月 計画書承認・校正・計画書完成／3月 契約完了</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="J37" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J37" s="21" t="inlineStr">
+      <c r="K37" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K37" s="19" t="n">
+      <c r="L37" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="20" t="n">
+      <c r="M37" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M37" s="16" t="inlineStr">
+      <c r="N37" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N37" s="16" t="inlineStr">
+      <c r="O37" s="16" t="inlineStr">
         <is>
           <t>素案の確定</t>
         </is>
@@ -4722,48 +5543,53 @@
           <t>実施要領、意見提出様式、対応表</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>B4 パブリックコメントの実施支援</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>仕様書5(5)</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>【5(5)】パブリックコメントの実施支援。計画素案がほぼ完成した段階で、町ウェブサイトを活用したパブリックコメントの実施を支援（実施アドバイス、意見への対応検討）し、結果を計画案へ反映する。パブリックコメントの実施時期については、当町と協議の上、決定することとする。</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="I38" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I38" s="17" t="inlineStr">
+      <c r="J38" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J38" s="18" t="inlineStr">
+      <c r="K38" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K38" s="19" t="n">
+      <c r="L38" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="L38" s="20" t="n">
+      <c r="M38" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M38" s="16" t="inlineStr">
+      <c r="N38" s="16" t="inlineStr">
         <is>
           <t>計画策定業務設計書 第4章（高齢者計画と共通）</t>
         </is>
       </c>
-      <c r="N38" s="16" t="inlineStr">
+      <c r="O38" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4790,49 +5616,54 @@
           <t>意見提出期間1か月</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>B4 パブリックコメントの実施支援</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>仕様書5(5)・7</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>【5(5)】パブリックコメントの実施支援。計画素案がほぼ完成した段階で、町ウェブサイトを活用したパブリックコメントの実施を支援（実施アドバイス、意見への対応検討）し、結果を計画案へ反映する。パブリックコメントの実施時期については、当町と協議の上、決定することとする。
 【7】スケジュール。6月 業者選定・契約締結／〜7月 アンケート調査・統計整理／〜8月 アンケート調査・課題分析（自立支援協議会による検討）／9月 骨子案作成／10月 骨子案検討（自立支援協議会による検討）／〜12月 素案作成／〜1月 素案検討（自立支援協議会による検討・パブリックコメントの実施）／〜2月 計画書承認・校正・計画書完成／3月 契約完了</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr">
+      <c r="H39" s="17" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr">
+      <c r="I39" s="17" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="I39" s="17" t="inlineStr">
+      <c r="J39" s="17" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="J39" s="21" t="inlineStr">
+      <c r="K39" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K39" s="19" t="n">
+      <c r="L39" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="20" t="n">
+      <c r="M39" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M39" s="16" t="inlineStr">
+      <c r="N39" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N39" s="16" t="inlineStr">
+      <c r="O39" s="16" t="inlineStr">
         <is>
           <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
@@ -4859,48 +5690,53 @@
           <t>意見の整理、対応案の作成、計画への反映</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>B4 パブリックコメントの実施支援</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>仕様書5(5)</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>【5(5)】パブリックコメントの実施支援。計画素案がほぼ完成した段階で、町ウェブサイトを活用したパブリックコメントの実施を支援（実施アドバイス、意見への対応検討）し、結果を計画案へ反映する。パブリックコメントの実施時期については、当町と協議の上、決定することとする。</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H40" s="17" t="inlineStr">
+      <c r="I40" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I40" s="17" t="inlineStr">
+      <c r="J40" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J40" s="21" t="inlineStr">
+      <c r="K40" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K40" s="19" t="n">
+      <c r="L40" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="20" t="n">
+      <c r="M40" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M40" s="16" t="inlineStr">
+      <c r="N40" s="16" t="inlineStr">
         <is>
           <t>対応表の様式は作成済み</t>
         </is>
       </c>
-      <c r="N40" s="16" t="inlineStr">
+      <c r="O40" s="16" t="inlineStr">
         <is>
           <t>パブコメの実施</t>
         </is>
@@ -4927,48 +5763,53 @@
           <t>仕様書8②により3回と明記</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>B6 業務管理・打合せ</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>仕様書8②</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>【8②】当町で開催する自立支援協議会（3回）に出席し、計画の説明をする。</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="H41" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H41" s="17" t="inlineStr">
+      <c r="I41" s="17" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="J41" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J41" s="20" t="inlineStr">
+      <c r="K41" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K41" s="19" t="n">
+      <c r="L41" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="L41" s="20" t="n">
+      <c r="M41" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M41" s="16" t="inlineStr">
+      <c r="N41" s="16" t="inlineStr">
         <is>
           <t>第1回は令和8年8月19日（資料第3版を作成済み）</t>
         </is>
       </c>
-      <c r="N41" s="16" t="inlineStr">
+      <c r="O41" s="16" t="inlineStr">
         <is>
           <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
@@ -4995,48 +5836,53 @@
           <t>パブリックコメント対応後の計画案</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>B3 計画策定支援業務</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>仕様書5(4)</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>【5(4)】計画策定支援業務。（3）の現状分析や課題、並びに国及び県が示す関連指針や計画等を踏まえ、以下の計画の計画骨子案、計画素案、計画案の作成など、計画の策定支援を行う。①障がい者計画（令和9年度から11年度を計画期間とし、基本理念や基本目標のほか、障がい者支援全般に係る施策を策定する）②第4期障がい児福祉計画・第8期障がい福祉計画（施設入所者の地域生活への移行などの成果目標、生活介護の利用者数などの活動指標について、統計的手法を駆使して設定した内容への助言をする。また、障がい福祉サービス、地域生活支援事業などについて、当該年度ごと、サービス種類ごとの見込量を推計し、目標値の設定及び目標達成のための施策の検討を行う）</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="H42" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H42" s="17" t="inlineStr">
+      <c r="I42" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="J42" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J42" s="21" t="inlineStr">
+      <c r="K42" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K42" s="19" t="n">
+      <c r="L42" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="20" t="n">
+      <c r="M42" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M42" s="16" t="inlineStr">
+      <c r="N42" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N42" s="16" t="inlineStr">
+      <c r="O42" s="16" t="inlineStr">
         <is>
           <t>意見への対応</t>
         </is>
@@ -5063,48 +5909,53 @@
           <t>**仕様書は「原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む」と定める**</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>B5 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>仕様書6 成果品②</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>【成果品②】②障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画　電子データ。※原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む。※電子データはMicrosoft Word 2019以上の形式で収録すること。</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="H43" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H43" s="17" t="inlineStr">
+      <c r="I43" s="17" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="J43" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J43" s="21" t="inlineStr">
+      <c r="K43" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K43" s="19" t="n">
+      <c r="L43" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="20" t="n">
+      <c r="M43" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="M43" s="16" t="inlineStr">
+      <c r="N43" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N43" s="16" t="inlineStr">
+      <c r="O43" s="16" t="inlineStr">
         <is>
           <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
@@ -5131,48 +5982,53 @@
           <t>読みやすさの調整</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>B5 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
         <is>
           <t>仕様書6 成果品②</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>【成果品②】②障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画　電子データ。※原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む。※電子データはMicrosoft Word 2019以上の形式で収録すること。</t>
         </is>
       </c>
-      <c r="G44" s="17" t="inlineStr">
+      <c r="H44" s="17" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H44" s="17" t="inlineStr">
+      <c r="I44" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I44" s="17" t="inlineStr">
+      <c r="J44" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J44" s="21" t="inlineStr">
+      <c r="K44" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K44" s="19" t="n">
+      <c r="L44" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="20" t="n">
+      <c r="M44" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="M44" s="16" t="inlineStr">
+      <c r="N44" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N44" s="16" t="inlineStr">
+      <c r="O44" s="16" t="inlineStr">
         <is>
           <t>計画案の確定</t>
         </is>
@@ -5199,56 +6055,61 @@
           <t>電子データ（Microsoft Word 2019以上の形式）。**印刷の指定はなし**</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>B5 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>仕様書6 成果品②</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>【成果品②】②障がい者計画・第4期障がい児福祉計画・第8期障がい福祉計画　電子データ。※原稿作成、レイアウトデザイン（イラスト起こし数点）、リライト作業を含む。※電子データはMicrosoft Word 2019以上の形式で収録すること。</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
+      <c r="H45" s="17" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H45" s="17" t="inlineStr">
+      <c r="I45" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I45" s="17" t="inlineStr">
+      <c r="J45" s="17" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J45" s="21" t="inlineStr">
+      <c r="K45" s="21" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K45" s="19" t="n">
+      <c r="L45" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="20" t="n">
+      <c r="M45" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="M45" s="16" t="inlineStr">
+      <c r="N45" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N45" s="16" t="inlineStr">
+      <c r="O45" s="16" t="inlineStr">
         <is>
           <t>**完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）**</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N45"/>
-  <conditionalFormatting sqref="K2:K45">
+  <autoFilter ref="A1:O45"/>
+  <conditionalFormatting sqref="L2:L45">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>100</formula>
     </cfRule>
@@ -5257,10 +6118,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J2:J45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,進行中,要対応,データ待ち,未着手"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -5359,27 +6220,27 @@
         <v/>
       </c>
       <c r="C2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A2,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A2)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I2" s="17" t="inlineStr">
@@ -5409,27 +6270,27 @@
         <v/>
       </c>
       <c r="C3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A3,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A3)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I3" s="17" t="inlineStr">
@@ -5459,27 +6320,27 @@
         <v/>
       </c>
       <c r="C4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A4,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A4)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I4" s="17" t="inlineStr">
@@ -5509,27 +6370,27 @@
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A5,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A5)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -5559,27 +6420,27 @@
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A6,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A6)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I6" s="17" t="inlineStr">
@@ -5609,27 +6470,27 @@
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A7,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A7)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -5659,27 +6520,27 @@
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A8,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A8)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -5709,27 +6570,27 @@
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$K$2:$K$45,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$K$2:$K$45,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$K$2:$K$45,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$K$2:$K$45,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$J$2:$J$45,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$45,$A9,'01_WBS'!$K$2:$K$45,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="24">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$K$2:$K$45*'01_WBS'!$L$2:$L$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$L$2:$L$45*'01_WBS'!$M$2:$M$45)/SUMPRODUCT(('01_WBS'!$A$2:$A$45=$A9)*'01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I9" s="17" t="inlineStr">
@@ -5779,7 +6640,7 @@
         <v/>
       </c>
       <c r="H10" s="27">
-        <f>IF(SUM('01_WBS'!$L$2:$L$45)=0,0,SUMPRODUCT('01_WBS'!$K$2:$K$45,'01_WBS'!$L$2:$L$45)/SUM('01_WBS'!$L$2:$L$45)/100)</f>
+        <f>IF(SUM('01_WBS'!$M$2:$M$45)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$45,'01_WBS'!$M$2:$M$45)/SUM('01_WBS'!$M$2:$M$45)/100)</f>
         <v/>
       </c>
       <c r="I10" s="17" t="inlineStr">
